--- a/stories/arbres/ATOM-TMP.SAI.001-04.xlsx
+++ b/stories/arbres/ATOM-TMP.SAI.001-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Noémie marche dans le jardin avec maman. Maman dit : il y a quatre saisons. Au printemps, Noémie voit des fleurs. Les fleurs sentent bon. En été, il fait chaud. Noémie boit de l'eau. En automne, les feuilles tombent. Elles sont jaunes. En hiver, Noémie met son manteau. Le manteau est doux. Maman dit un signe chacune. Fleurs, chaud, feuilles, manteau. Noémie répète : quatre saisons. Printemps, été, automne, hiver. Parce qu'il fait un peu frais, Noémie touche une feuille sèche. Maman dit : c'est l'automne. Un signe chacune. Noémie sourit.</t>
+          <t>Noémie marche dans le jardin avec maman. Il y a quatre saisons. Au printemps, Noémie voit des fleurs. Les fleurs sentent bon. En été, il fait chaud. Noémie boit de l'eau. En automne, les feuilles tombent. Elles sont jaunes. En hiver, Noémie met son manteau. Le manteau est doux. Maman dit un signe chacune. Fleurs, chaud, feuilles, manteau. Noémie répète : quatre saisons. Printemps, été, automne, hiver. Parce qu'il fait un peu frais, Noémie touche une feuille sèche. C'est l'automne. Un signe chacune. Noémie sourit.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Noémie marche dans le jardin avec maman.
+maman|Il y a quatre saisons. Au printemps, Noémie voit des fleurs.
+narrateur|Les fleurs sentent bon. En été, il fait chaud. Noémie boit de l'eau. En automne, les feuilles tombent. Elles sont jaunes. En hiver, Noémie met son manteau. Le manteau est doux. Maman dit un signe chacune. Fleurs, chaud, feuilles, manteau. Noémie répète : quatre saisons. Printemps, été, automne, hiver. Parce qu'il fait un peu frais, Noémie touche une feuille sèche.
+maman|C'est l'automne.
+narrateur|Un signe chacune. Noémie sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1490,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Les feuilles tombent. Quelle saison est-ce ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1663,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Noémie a nommé les quatre saisons. Un signe chacune. Maman l'a aidée.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1830,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Noémie ramasse une feuille jaune. Maman tient sa main.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1997,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2037,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-TMP.SAI.001-04.xlsx
+++ b/stories/arbres/ATOM-TMP.SAI.001-04.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,11 @@
 narrateur|Un signe chacune. Noémie sourit.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1497,6 +1507,7 @@
           <t>narrateur|Les feuilles tombent. Quelle saison est-ce ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1668,6 +1679,7 @@
           <t>narrateur|Noémie a nommé les quatre saisons. Un signe chacune. Maman l'a aidée.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1835,6 +1847,7 @@
           <t>narrateur|Noémie ramasse une feuille jaune. Maman tient sa main.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2002,6 +2015,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2020,7 +2034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2044,6 +2058,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2245,6 +2273,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-TMP.SAI.001-04.xlsx
+++ b/stories/arbres/ATOM-TMP.SAI.001-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Noémie nomme les quatre saisons</t>
+          <t>Les criquets de Nina</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Nina veut écouter les criquets dans le jardin chaud. L'orage arrive. Elles attendent sous l'auvent. La lumière revient, les criquets aussi.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Noémie marche dans le jardin avec maman. Il y a quatre saisons. Au printemps, Noémie voit des fleurs. Les fleurs sentent bon. En été, il fait chaud. Noémie boit de l'eau. En automne, les feuilles tombent. Elles sont jaunes. En hiver, Noémie met son manteau. Le manteau est doux. Maman dit un signe chacune. Fleurs, chaud, feuilles, manteau. Noémie répète : quatre saisons. Printemps, été, automne, hiver. Parce qu'il fait un peu frais, Noémie touche une feuille sèche. C'est l'automne. Un signe chacune. Noémie sourit.</t>
+          <t>L'air de la cuisine est lourd, presque collant. Les volets laissent une bande de soleil. Ça sent l'abricot, sur l'assiette. Nina a les genoux chauds, déjà. On va au jardin ? Oui. Les dalles sont chaudes, attention. En ce moment, Nina pousse la porte. L'air dehors est encore plus lourd. Un criquet chante près du mur. Tu l'entends, Nina ? Je l'entends. Il aime le chaud. Nina s'assoit sur la marche. La pierre brûle un peu les cuisses. Elle pose l'abricot à côté. Encore un criquet. Ils sont plusieurs, dans l'herbe sèche. Le ciel, au fond, devient gris. Un vent court passe, tout sec. Les feuilles du figuier se retournent. Il va pleuvoir ? Un orage, je crois. Un grognement arrive, loin. Nina serre l'abricot. On va sous l'auvent. Elles reculent de deux pas. La première goutte tape le zinc. Toc. Puis beaucoup, toutes ensemble. Les criquets ? Ils se taisent, le temps de la pluie. L'eau court sur les dalles chaudes. Ça sent la terre mouillée, tout fort. L'abricot a une goutte sur la peau. Mon abricot est mouillé. On l'essuie, après. Le tonnerre passe au-dessus du toit. Nina se colle un peu à maman. On attend la lumière. La pluie ralentit, puis s'arrête. Un rayon revient sur le figuier. Les feuilles brillent, toutes neuves. C'est fini ? Oui. Écoute. Un criquet recommence, tout près. Il est là ! L'été reprend, après l'orage.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Noémie marche dans le jardin avec maman. Maman dit : il y a &lt;emphasis level="moderate"&gt;quatre&lt;/emphasis&gt; saisons. Au printemps, Noémie voit des fleurs. Les fleurs sentent bon. En été, il fait chaud. Noémie boit de l'eau. En automne, les feuilles tombent. Elles sont jaunes. En hiver, Noémie met son manteau. Le manteau est doux. Maman dit un signe chacune. Fleurs, chaud, feuilles, manteau. Noémie répète : quatre saisons. Printemps, été, automne, hiver. Parce qu'il fait un peu frais, Noémie touche une feuille sèche. Maman dit : c'est l'automne. Un signe chacune. Noémie sourit.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>L'air de la cuisine est lourd, presque collant. Les volets laissent une bande de soleil. Ça sent l'abricot, sur l'assiette. Nina a les genoux chauds, déjà. On va au jardin ? Oui. Les dalles sont chaudes, attention. En ce moment, Nina pousse la porte. L'air dehors est encore plus lourd. Un criquet chante près du mur. Tu l'entends, Nina ? Je l'entends. Il aime le chaud. Nina s'assoit sur la marche. La pierre brûle un peu les cuisses. Elle pose l'abricot à côté. Encore un criquet. Ils sont plusieurs, dans l'herbe sèche. Le ciel, au fond, devient gris. Un vent court passe, tout sec. Les feuilles du figuier se retournent. Il va pleuvoir ? Un orage, je crois. Un grognement arrive, loin. Nina serre l'abricot. On va sous l'auvent. Elles reculent de deux pas. La première goutte tape le zinc. Toc. Puis beaucoup, toutes ensemble. Les criquets ? Ils se taisent, le temps de la pluie. L'eau court sur les dalles chaudes. Ça sent la terre mouillée, tout fort. L'abricot a une goutte sur la peau. Mon abricot est mouillé. On l'essuie, après. Le tonnerre passe au-dessus du toit. Nina se colle un peu à maman. On attend la lumière. La pluie ralentit, puis s'arrête. Un rayon revient sur le figuier. Les feuilles brillent, toutes neuves. C'est fini ? Oui. Écoute. Un criquet recommence, tout près. Il est là ! L'été reprend, après l'orage.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.92</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,11 +1324,55 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Noémie marche dans le jardin avec maman.
-maman|Il y a quatre saisons. Au printemps, Noémie voit des fleurs.
-narrateur|Les fleurs sentent bon. En été, il fait chaud. Noémie boit de l'eau. En automne, les feuilles tombent. Elles sont jaunes. En hiver, Noémie met son manteau. Le manteau est doux. Maman dit un signe chacune. Fleurs, chaud, feuilles, manteau. Noémie répète : quatre saisons. Printemps, été, automne, hiver. Parce qu'il fait un peu frais, Noémie touche une feuille sèche.
-maman|C'est l'automne.
-narrateur|Un signe chacune. Noémie sourit.</t>
+          <t>narrateur|L'air de la cuisine est lourd, presque collant.
+narrateur|Les volets laissent une bande de soleil.
+narrateur|Ça sent l'abricot, sur l'assiette.
+narrateur|Nina a les genoux chauds, déjà.
+enfant-f|On va au jardin ?
+maman|Oui.
+maman|Les dalles sont chaudes, attention.
+narrateur|En ce moment, Nina pousse la porte.
+narrateur|L'air dehors est encore plus lourd.
+narrateur|Un criquet chante près du mur.
+maman|Tu l'entends, Nina ?
+enfant-f|Je l'entends.
+maman|Il aime le chaud.
+narrateur|Nina s'assoit sur la marche.
+narrateur|La pierre brûle un peu les cuisses.
+narrateur|Elle pose l'abricot à côté.
+enfant-f|Encore un criquet.
+maman|Ils sont plusieurs, dans l'herbe sèche.
+narrateur|Le ciel, au fond, devient gris.
+narrateur|Un vent court passe, tout sec.
+narrateur|Les feuilles du figuier se retournent.
+enfant-f|Il va pleuvoir ?
+maman|Un orage, je crois.
+narrateur|Un grognement arrive, loin.
+narrateur|Nina serre l'abricot.
+maman|On va sous l'auvent.
+narrateur|Elles reculent de deux pas.
+narrateur|La première goutte tape le zinc.
+narrateur|Toc.
+narrateur|Puis beaucoup, toutes ensemble.
+enfant-f|Les criquets ?
+maman|Ils se taisent, le temps de la pluie.
+narrateur|L'eau court sur les dalles chaudes.
+narrateur|Ça sent la terre mouillée, tout fort.
+narrateur|L'abricot a une goutte sur la peau.
+enfant-f|Mon abricot est mouillé.
+maman|On l'essuie, après.
+narrateur|Le tonnerre passe au-dessus du toit.
+narrateur|Nina se colle un peu à maman.
+maman|On attend la lumière.
+narrateur|La pluie ralentit, puis s'arrête.
+narrateur|Un rayon revient sur le figuier.
+narrateur|Les feuilles brillent, toutes neuves.
+enfant-f|C'est fini ?
+maman|Oui.
+maman|Écoute.
+narrateur|Un criquet recommence, tout près.
+enfant-f|Il est là !
+maman|L'été reprend, après l'orage.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1348,12 +1404,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Les feuilles tombent. Quelle saison est-ce ?</t>
+          <t>Il fait chaud, les criquets chantent. Quelle saison est-ce ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Les feuilles tombent. Quelle saison est-ce ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Il fait chaud, les criquets chantent. Quelle saison est-ce ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1363,12 +1419,12 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>automne</t>
+          <t>été</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>automne | l'automne | en automne</t>
+          <t>été | l'été | en été | chaud | criquets</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1383,7 +1439,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>En automne, les feuilles tombent. Quelle saison ?</t>
+          <t>Il fait chaud, les criquets chantent. Quelle saison ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1432,7 +1488,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1504,10 +1560,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Les feuilles tombent. Quelle saison est-ce ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Il fait chaud, les criquets chantent.
+narrateur|Quelle saison est-ce ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1532,12 +1588,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Noémie a nommé les quatre saisons. Un signe chacune. Maman l'a aidée.</t>
+          <t>Nina essuie l'abricot sur sa robe. Une tache d'eau reste, toute claire. Il est encore bon. Oui. Tu as attendu sous l'auvent. Les dalles fument un peu, au soleil. Ça sent le chaud et l'eau, ensemble. Encore un criquet. Bravo, Nina. Tu l'as entendu revenir. Le figuier goutte encore, une feuille.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Noémie a nommé les &lt;emphasis level="moderate"&gt;quatre&lt;/emphasis&gt; saisons. Un signe chacune. Maman l'a aidée.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina essuie l'abricot sur sa robe. Une tache d'eau reste, toute claire. Il est encore bon. Oui. Tu as attendu sous l'auvent. Les dalles fument un peu, au soleil. Ça sent le chaud et l'eau, ensemble. Encore un criquet. Bravo, Nina. Tu l'as entendu revenir. Le figuier goutte encore, une feuille.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1600,7 +1656,7 @@
         <v>0.92</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1676,10 +1732,19 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Noémie a nommé les quatre saisons. Un signe chacune. Maman l'a aidée.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Nina essuie l'abricot sur sa robe.
+narrateur|Une tache d'eau reste, toute claire.
+enfant-f|Il est encore bon.
+maman|Oui.
+maman|Tu as attendu sous l'auvent.
+narrateur|Les dalles fument un peu, au soleil.
+narrateur|Ça sent le chaud et l'eau, ensemble.
+enfant-f|Encore un criquet.
+maman|Bravo, Nina.
+maman|Tu l'as entendu revenir.
+narrateur|Le figuier goutte encore, une feuille.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1704,12 +1769,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Noémie ramasse une feuille jaune. Maman tient sa main.</t>
+          <t>Elles restent sur la marche. La pierre est plus douce, maintenant. L'orage est parti. Et la lumière est revenue. Nina croque l'abricot. Le jus est tiède, un peu sucré. C'est l'été, dans notre jardin.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Noémie ramasse &lt;emphasis level="moderate"&gt;un&lt;/emphasis&gt;e feuille jaune. Maman tient sa main.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Elles restent sur la marche. La pierre est plus douce, maintenant. L'orage est parti. Et la lumière est revenue. Nina croque l'abricot. Le jus est tiède, un peu sucré. C'est l'été, dans notre jardin.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1772,7 +1837,7 @@
         <v>0.92</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1844,10 +1909,15 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Noémie ramasse une feuille jaune. Maman tient sa main.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Elles restent sur la marche.
+narrateur|La pierre est plus douce, maintenant.
+enfant-f|L'orage est parti.
+maman|Et la lumière est revenue.
+narrateur|Nina croque l'abricot.
+narrateur|Le jus est tiède, un peu sucré.
+maman|C'est l'été, dans notre jardin.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1872,12 +1942,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le zinc sèche, tout lentement. Un criquet chante encore près du mur. Je reste un peu. Oui. La bande de soleil a grandi sur le sol. Nina pose le noyau sur la marche chaude.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le zinc sèche, tout lentement. Un criquet chante encore près du mur. Je reste un peu. Oui. La bande de soleil a grandi sur le sol. Nina pose le noyau sur la marche chaude.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1933,14 +2003,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2012,10 +2082,14 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Le zinc sèche, tout lentement.
+narrateur|Un criquet chante encore près du mur.
+enfant-f|Je reste un peu.
+maman|Oui.
+narrateur|La bande de soleil a grandi sur le sol.
+narrateur|Nina pose le noyau sur la marche chaude.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2034,7 +2108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2072,6 +2146,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-TMP.SAI.001-04.xlsx
+++ b/stories/arbres/ATOM-TMP.SAI.001-04.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>jardin</t>
+          <t>jardin d'été, auvent, orage</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Noémie, maman</t>
+          <t>Nina, maman</t>
         </is>
       </c>
     </row>
